--- a/public/downloads/GrewalHighly2019.xlsx
+++ b/public/downloads/GrewalHighly2019.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,10 +169,31 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>O</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>HO</t>
+  </si>
+  <si>
+    <t>O</t>
   </si>
   <si>
     <t>HO2</t>
@@ -659,10 +682,10 @@
         <v>37</v>
       </c>
       <c r="N3" s="5">
-        <v>558.476891040802</v>
+        <v>558476.891040802</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03418269623214604</v>
+        <v>34.18269623214604</v>
       </c>
       <c r="P3" s="5">
         <v>16338</v>
@@ -709,10 +732,10 @@
         <v>37</v>
       </c>
       <c r="N4" s="5">
-        <v>749.335476398468</v>
+        <v>749335.476398468</v>
       </c>
       <c r="O4" s="4">
-        <v>0.09512955140262384</v>
+        <v>95.12955140262385</v>
       </c>
       <c r="P4" s="5">
         <v>7877</v>
@@ -759,10 +782,10 @@
         <v>37</v>
       </c>
       <c r="N5" s="5">
-        <v>675.6091914176941</v>
+        <v>675609.1914176941</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1700073456008289</v>
+        <v>170.0073456008289</v>
       </c>
       <c r="P5" s="5">
         <v>3974</v>
@@ -809,10 +832,10 @@
         <v>37</v>
       </c>
       <c r="N6" s="5">
-        <v>364.0211555957794</v>
+        <v>364021.1555957794</v>
       </c>
       <c r="O6" s="4">
-        <v>0.09283885631108886</v>
+        <v>92.83885631108886</v>
       </c>
       <c r="P6" s="5">
         <v>3921</v>
@@ -859,10 +882,10 @@
         <v>37</v>
       </c>
       <c r="N7" s="5">
-        <v>751.1432349681854</v>
+        <v>751143.2349681854</v>
       </c>
       <c r="O7" s="4">
-        <v>0.3055912265940543</v>
+        <v>305.5912265940543</v>
       </c>
       <c r="P7" s="5">
         <v>2458</v>
@@ -909,10 +932,10 @@
         <v>37</v>
       </c>
       <c r="N8" s="5">
-        <v>125.4246127605438</v>
+        <v>125424.6127605438</v>
       </c>
       <c r="O8" s="4">
-        <v>0.02903347517605181</v>
+        <v>29.03347517605181</v>
       </c>
       <c r="P8" s="5">
         <v>4320</v>
@@ -959,10 +982,10 @@
         <v>37</v>
       </c>
       <c r="N9" s="5">
-        <v>152.4982495307922</v>
+        <v>152498.2495307922</v>
       </c>
       <c r="O9" s="4">
-        <v>0.0360175364975891</v>
+        <v>36.0175364975891</v>
       </c>
       <c r="P9" s="5">
         <v>4234</v>
@@ -1009,10 +1032,10 @@
         <v>37</v>
       </c>
       <c r="N10" s="5">
-        <v>230.5980863571167</v>
+        <v>230598.0863571167</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08685426981435657</v>
+        <v>86.85426981435657</v>
       </c>
       <c r="P10" s="5">
         <v>2655</v>
@@ -1059,10 +1082,10 @@
         <v>37</v>
       </c>
       <c r="N11" s="5">
-        <v>190.5151612758636</v>
+        <v>190515.1612758636</v>
       </c>
       <c r="O11" s="4">
-        <v>0.05044086875188341</v>
+        <v>50.44086875188341</v>
       </c>
       <c r="P11" s="5">
         <v>3777</v>
@@ -1109,10 +1132,10 @@
         <v>37</v>
       </c>
       <c r="N12" s="5">
-        <v>101.9077589511871</v>
+        <v>101907.7589511871</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02384922980369462</v>
+        <v>23.84922980369462</v>
       </c>
       <c r="P12" s="5">
         <v>4273</v>
@@ -1159,10 +1182,10 @@
         <v>37</v>
       </c>
       <c r="N13" s="5">
-        <v>308.3160121440887</v>
+        <v>308316.0121440887</v>
       </c>
       <c r="O13" s="4">
-        <v>0.08212999790732252</v>
+        <v>82.12999790732252</v>
       </c>
       <c r="P13" s="5">
         <v>3754</v>
@@ -1209,10 +1232,10 @@
         <v>37</v>
       </c>
       <c r="N14" s="5">
-        <v>2038.934678077698</v>
+        <v>2038934.678077698</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3403897626173118</v>
+        <v>340.3897626173118</v>
       </c>
       <c r="P14" s="5">
         <v>5990</v>
@@ -1259,10 +1282,10 @@
         <v>37</v>
       </c>
       <c r="N15" s="5">
-        <v>806.5425078868866</v>
+        <v>806542.5078868866</v>
       </c>
       <c r="O15" s="4">
-        <v>0.4133995427405877</v>
+        <v>413.3995427405877</v>
       </c>
       <c r="P15" s="5">
         <v>1951</v>
@@ -1309,10 +1332,10 @@
         <v>37</v>
       </c>
       <c r="N16" s="5">
-        <v>628.819988489151</v>
+        <v>628819.988489151</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1059868512538599</v>
+        <v>105.9868512538599</v>
       </c>
       <c r="P16" s="5">
         <v>5933</v>
@@ -1359,10 +1382,10 @@
         <v>37</v>
       </c>
       <c r="N17" s="5">
-        <v>281.7253234386444</v>
+        <v>281725.3234386444</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1061512145586452</v>
+        <v>106.1512145586452</v>
       </c>
       <c r="P17" s="5">
         <v>2654</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,66 +1497,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.124194901383556</v>
+        <v>0.3014534870417961</v>
       </c>
       <c r="C3" s="4">
-        <v>0.124194901383556</v>
+        <v>0.320886492086869</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1124968840923127</v>
+        <v>0.2816534821313113</v>
       </c>
       <c r="E3" s="4">
-        <v>93.21821036106749</v>
+        <v>87.21350078492934</v>
       </c>
       <c r="F3" s="4">
-        <v>92.43417656169281</v>
+        <v>87.28187919463082</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.00455466592896188</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3011031281241837</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3196443104698793</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2185580622591403</v>
+        <v>0.2144891386090732</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1624554004377336</v>
+        <v>0.1552263564765507</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1420870070398195</v>
+        <v>0.1738239753765995</v>
       </c>
       <c r="E4" s="4">
-        <v>92.50392464678177</v>
+        <v>87.21873364730507</v>
       </c>
       <c r="F4" s="4">
-        <v>90.24866632249335</v>
+        <v>86.92651867148528</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
@@ -1528,64 +1601,100 @@
         <v>11</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1362650863984908</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1533156729448369</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.107705912763997</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1876652928968509</v>
+        <v>0.4201031444182154</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1707384595067268</v>
+        <v>0.3071998136110192</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1657289170127007</v>
+        <v>0.3827695401135152</v>
       </c>
       <c r="E5" s="4">
-        <v>90.04947433518802</v>
+        <v>80.7142857142851</v>
       </c>
       <c r="F5" s="4">
-        <v>89.29530201342196</v>
+        <v>77.05308114704002</v>
       </c>
       <c r="G5" s="5">
         <v>11</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2209853788996794</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4236782923917071</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2292461249871904</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,75 +1797,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3760659294664689</v>
+        <v>0.3718204825305716</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1912123574132223</v>
+        <v>0.3758384462630687</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2712864559222991</v>
+        <v>0.3474804236752024</v>
       </c>
       <c r="E3" s="4">
-        <v>90.39246467817894</v>
+        <v>86.02040816326522</v>
       </c>
       <c r="F3" s="4">
-        <v>86.74152469454485</v>
+        <v>85.26329375322685</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.01988258396594631</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3737547320706148</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3803412290617195</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2937982356730821</v>
+        <v>0.4709216349330522</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1998532624837258</v>
+        <v>0.4709216349330522</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2363874982789014</v>
+        <v>0.4547005884852983</v>
       </c>
       <c r="E4" s="4">
-        <v>90.89481946624801</v>
+        <v>87.29199372056515</v>
       </c>
       <c r="F4" s="4">
-        <v>90.13939081053122</v>
+        <v>87.94785751161562</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1755,25 +1915,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.02554609051186346</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4689565510475243</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4689565510475243</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3346810894875112</v>
+        <v>0.485898271964699</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2914545765099845</v>
+        <v>0.3312568830703455</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2942887773509478</v>
+        <v>0.6095856722004075</v>
       </c>
       <c r="E5" s="4">
-        <v>87.15213358070501</v>
+        <v>85.45763760049473</v>
       </c>
       <c r="F5" s="4">
-        <v>76.44295302013414</v>
+        <v>77.97844213951561</v>
       </c>
       <c r="G5" s="5">
         <v>11</v>
@@ -1782,23 +1960,41 @@
         <v>8</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2270926660967874</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4138864360870897</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2606271920007313</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,66 +2097,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3929594631890482</v>
+        <v>0.2185580622591403</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1397001210614645</v>
+        <v>0.1624554004377336</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1872494255149556</v>
+        <v>0.1420870070398195</v>
       </c>
       <c r="E3" s="4">
-        <v>91.12506541077967</v>
+        <v>92.50392464678177</v>
       </c>
       <c r="F3" s="4">
-        <v>86.14524178282564</v>
+        <v>90.24866632249335</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1267003406779184</v>
+      </c>
+      <c r="O3" s="5">
+        <v>11</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1625831121057453</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1058971000573586</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2586383774647126</v>
+        <v>0.124194901383556</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2586383774647126</v>
+        <v>0.124194901383556</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2566345610068175</v>
+        <v>0.1124968840923127</v>
       </c>
       <c r="E4" s="4">
-        <v>92.11407639979069</v>
+        <v>93.21821036106749</v>
       </c>
       <c r="F4" s="4">
-        <v>91.84305627258638</v>
+        <v>92.43417656169281</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
@@ -1968,50 +2215,86 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1179564969620081</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09332336342422322</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09332336342422322</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2988299536596706</v>
+        <v>0.1876652928968509</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3305690873337205</v>
+        <v>0.1707384595067268</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2901800368450386</v>
+        <v>0.1657289170127007</v>
       </c>
       <c r="E5" s="4">
-        <v>88.05813234384642</v>
+        <v>90.04947433518802</v>
       </c>
       <c r="F5" s="4">
-        <v>87.69676632092714</v>
+        <v>89.29530201342196</v>
       </c>
       <c r="G5" s="5">
         <v>11</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="5">
         <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1142442108926588</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1341774502960652</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1233262537351284</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,25 +2397,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3478263126481828</v>
+        <v>0.2937982356730821</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3069366059248869</v>
+        <v>0.1998532624837258</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2801982958095222</v>
+        <v>0.2363874982789014</v>
       </c>
       <c r="E3" s="4">
-        <v>89.36682365253795</v>
+        <v>90.89481946624801</v>
       </c>
       <c r="F3" s="4">
-        <v>86.39046635690943</v>
+        <v>90.13939081053122</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
@@ -2126,89 +2442,125 @@
         <v>12</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.0388693512076775</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2908082855801839</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1933750372824462</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2977036481537534</v>
+        <v>0.3760659294664689</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1800630567956721</v>
+        <v>0.1912123574132223</v>
       </c>
       <c r="D4" s="4">
-        <v>0.196901684956491</v>
+        <v>0.2712864559222991</v>
       </c>
       <c r="E4" s="4">
-        <v>89.66248037676607</v>
+        <v>90.39246467817894</v>
       </c>
       <c r="F4" s="4">
-        <v>89.01049733264443</v>
+        <v>86.74152469454485</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.01668601463357401</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3747823898792709</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1927292678344562</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1876719109654681</v>
+        <v>0.3346810894875112</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1726624571218578</v>
+        <v>0.2914545765099845</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1875670760793598</v>
+        <v>0.2942887773509478</v>
       </c>
       <c r="E5" s="4">
-        <v>84.61966604823684</v>
+        <v>87.15213358070501</v>
       </c>
       <c r="F5" s="4">
-        <v>80.49420378279338</v>
+        <v>76.44295302013414</v>
       </c>
       <c r="G5" s="5">
         <v>11</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2222,9 +2574,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1664667616284063</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3107450048850295</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2348717629650832</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,107 +2697,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3146495638794595</v>
+        <v>0.2586383774647126</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1023737590670144</v>
+        <v>0.2586383774647126</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1536611048861528</v>
+        <v>0.2566345610068175</v>
       </c>
       <c r="E3" s="4">
-        <v>87.0722135007852</v>
+        <v>92.11407639979069</v>
       </c>
       <c r="F3" s="4">
-        <v>85.52056444673602</v>
+        <v>91.84305627258638</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.20353152080755</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1829528153453314</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1829528153453314</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1649035047132684</v>
+        <v>0.3929594631890482</v>
       </c>
       <c r="C4" s="4">
-        <v>0.09901963628662784</v>
+        <v>0.1397001210614645</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1356018338498013</v>
+        <v>0.1872494255149556</v>
       </c>
       <c r="E4" s="4">
-        <v>87.70538984824726</v>
+        <v>91.12506541077967</v>
       </c>
       <c r="F4" s="4">
-        <v>87.65961108243052</v>
+        <v>86.14524178282564</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
         <v>2</v>
       </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.008153519798993456</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.388641751438307</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1370872128877243</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1647450712583688</v>
+        <v>0.2988299536596706</v>
       </c>
       <c r="C5" s="4">
-        <v>0.145271440324645</v>
+        <v>0.3305690873337205</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1676313327077992</v>
+        <v>0.2901800368450386</v>
       </c>
       <c r="E5" s="4">
-        <v>84.71552257266552</v>
+        <v>88.05813234384642</v>
       </c>
       <c r="F5" s="4">
-        <v>87.17917429326785</v>
+        <v>87.69676632092714</v>
       </c>
       <c r="G5" s="5">
         <v>11</v>
@@ -2435,9 +2874,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1808436494333421</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2470830649482991</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.273146353517537</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,34 +2997,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2890922684858808</v>
+        <v>0.2977036481537534</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2890922684858808</v>
+        <v>0.1800630567956721</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2881795975801554</v>
+        <v>0.196901684956491</v>
       </c>
       <c r="E3" s="4">
-        <v>94.01098901098899</v>
+        <v>89.66248037676607</v>
       </c>
       <c r="F3" s="4">
-        <v>94.77542591636536</v>
+        <v>89.01049733264443</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2566,66 +3056,102 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1008862157071988</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2558467616932276</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1431252811057024</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3924718418312927</v>
+        <v>0.3478263126481828</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3924718418312927</v>
+        <v>0.3069366059248869</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3908074715327234</v>
+        <v>0.2801982958095222</v>
       </c>
       <c r="E4" s="4">
-        <v>93.8932496075353</v>
+        <v>89.36682365253795</v>
       </c>
       <c r="F4" s="4">
-        <v>94.72121837893634</v>
+        <v>86.39046635690943</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1175250070288148</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.286204057978525</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2499729139518254</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6939741555499181</v>
+        <v>0.1876719109654681</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6091966209738323</v>
+        <v>0.1726624571218578</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6286081583219559</v>
+        <v>0.1875670760793598</v>
       </c>
       <c r="E5" s="4">
-        <v>89.39084724798963</v>
+        <v>84.61966604823684</v>
       </c>
       <c r="F5" s="4">
-        <v>87.79743746186556</v>
+        <v>80.49420378279338</v>
       </c>
       <c r="G5" s="5">
         <v>11</v>
@@ -2648,9 +3174,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.05245829710125349</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2000573856782663</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.187800259548611</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,25 +3297,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5284359914897595</v>
+        <v>0.1649035047132684</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1572567276233254</v>
+        <v>0.09901963628662784</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2313468457560214</v>
+        <v>0.1356018338498013</v>
       </c>
       <c r="E3" s="4">
-        <v>86.00209314495031</v>
+        <v>87.70538984824726</v>
       </c>
       <c r="F3" s="4">
-        <v>82.11065221132233</v>
+        <v>87.65961108243052</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
@@ -2765,39 +3342,57 @@
         <v>10</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.07006799245865736</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.145301511657242</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08054384455965931</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5437348785517566</v>
+        <v>0.3146495638794595</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1750321536949674</v>
+        <v>0.1023737590670144</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1910338263759341</v>
+        <v>0.1536611048861528</v>
       </c>
       <c r="E4" s="4">
-        <v>85.74306645735221</v>
+        <v>87.0722135007852</v>
       </c>
       <c r="F4" s="4">
-        <v>85.64876957494371</v>
+        <v>85.52056444673602</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
@@ -2806,39 +3401,57 @@
         <v>10</v>
       </c>
       <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
         <v>2</v>
       </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.004840695012796914</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3142772027246289</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1014056200644551</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2311605874451588</v>
+        <v>0.1647450712583688</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2430092352338167</v>
+        <v>0.145271440324645</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2681353521222059</v>
+        <v>0.1676313327077992</v>
       </c>
       <c r="E5" s="4">
-        <v>81.45021645021605</v>
+        <v>84.71552257266552</v>
       </c>
       <c r="F5" s="4">
-        <v>82.357128330281</v>
+        <v>87.17917429326785</v>
       </c>
       <c r="G5" s="5">
         <v>11</v>
@@ -2847,23 +3460,41 @@
         <v>9</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1234496039221816</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1539585884670834</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1320879613575182</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,75 +3597,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2968415233730463</v>
+        <v>0.3924718418312927</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2721860610884841</v>
+        <v>0.3924718418312927</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2680293900237126</v>
+        <v>0.3908074715327234</v>
       </c>
       <c r="E3" s="4">
-        <v>92.96703296703296</v>
+        <v>93.8932496075353</v>
       </c>
       <c r="F3" s="4">
-        <v>91.52039235931842</v>
+        <v>94.72121837893634</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3924718418312927</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1145425451338265</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1145425451338265</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.313077305628602</v>
+        <v>0.2890922684858808</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2393048271930528</v>
+        <v>0.2890922684858808</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2329331822393657</v>
+        <v>0.2881795975801554</v>
       </c>
       <c r="E4" s="4">
-        <v>92.53532182103605</v>
+        <v>94.01098901098899</v>
       </c>
       <c r="F4" s="4">
-        <v>90.51884357253337</v>
+        <v>94.77542591636536</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -3033,34 +3715,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2890922684858808</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1017213773815874</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1017213773815874</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3844317407329647</v>
+        <v>0.6939741555499181</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3844317407329647</v>
+        <v>0.6091966209738323</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3577658526836461</v>
+        <v>0.6286081583219559</v>
       </c>
       <c r="E5" s="4">
-        <v>92.3098330241187</v>
+        <v>89.39084724798963</v>
       </c>
       <c r="F5" s="4">
-        <v>91.03518405531796</v>
+        <v>87.79743746186556</v>
       </c>
       <c r="G5" s="5">
         <v>11</v>
       </c>
       <c r="H5" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -3074,9 +3774,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.6091966209738323</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1914805337763497</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1304147768003226</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.5437348785517566</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1750321536949674</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1910338263759341</v>
+      </c>
+      <c r="E3" s="4">
+        <v>85.74306645735221</v>
+      </c>
+      <c r="F3" s="4">
+        <v>85.64876957494371</v>
+      </c>
+      <c r="G3" s="5">
+        <v>13</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.01224682374932335</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5465610686477543</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1750321536949674</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5284359914897595</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1572567276233254</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2313468457560214</v>
+      </c>
+      <c r="E4" s="4">
+        <v>86.00209314495031</v>
+      </c>
+      <c r="F4" s="4">
+        <v>82.11065221132233</v>
+      </c>
+      <c r="G4" s="5">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.006260776759032538</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5289175897019928</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1560045722715189</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2311605874451588</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2430092352338167</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2681353521222059</v>
+      </c>
+      <c r="E5" s="4">
+        <v>81.45021645021605</v>
+      </c>
+      <c r="F5" s="4">
+        <v>82.357128330281</v>
+      </c>
+      <c r="G5" s="5">
+        <v>11</v>
+      </c>
+      <c r="H5" s="5">
+        <v>9</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.1484313496688606</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1945234570273875</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.198230520278763</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.313077305628602</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2393048271930528</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2329331822393657</v>
+      </c>
+      <c r="E3" s="4">
+        <v>92.53532182103605</v>
+      </c>
+      <c r="F3" s="4">
+        <v>90.51884357253337</v>
+      </c>
+      <c r="G3" s="5">
+        <v>13</v>
+      </c>
+      <c r="H3" s="5">
+        <v>12</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.235761793892172</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1960323857886554</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1321529801907916</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2968415233730463</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2721860610884841</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2680293900237126</v>
+      </c>
+      <c r="E4" s="4">
+        <v>92.96703296703296</v>
+      </c>
+      <c r="F4" s="4">
+        <v>91.52039235931842</v>
+      </c>
+      <c r="G4" s="5">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2721860610884841</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1408941663535148</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1259252627413653</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3844317407329647</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3844317407329647</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3577658526836461</v>
+      </c>
+      <c r="E5" s="4">
+        <v>92.3098330241187</v>
+      </c>
+      <c r="F5" s="4">
+        <v>91.03518405531796</v>
+      </c>
+      <c r="G5" s="5">
+        <v>11</v>
+      </c>
+      <c r="H5" s="5">
+        <v>11</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.3844317407329647</v>
+      </c>
+      <c r="O5" s="5">
+        <v>11</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1597670010268184</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1597670010268184</v>
+      </c>
+      <c r="R5" s="5">
+        <v>11</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>67.56756756756756</v>
+      </c>
+      <c r="C3" s="3">
+        <v>13.51351351351351</v>
+      </c>
+      <c r="D3" s="3">
+        <v>18.91891891891892</v>
+      </c>
+      <c r="E3" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="F3" s="3">
+        <v>16.21621621621622</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4282621349018109</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.251232556783049</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.296099365614682</v>
+      </c>
+      <c r="K3" s="4">
+        <v>83.04467733039171</v>
+      </c>
+      <c r="L3" s="4">
+        <v>77.94909002962575</v>
+      </c>
+      <c r="M3" s="5">
+        <v>37</v>
+      </c>
+      <c r="N3" s="5">
+        <v>558476.891040802</v>
+      </c>
+      <c r="O3" s="4">
+        <v>34.18269623214604</v>
+      </c>
+      <c r="P3" s="5">
+        <v>16338</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>59.45945945945946</v>
+      </c>
+      <c r="C4" s="3">
+        <v>10.81081081081081</v>
+      </c>
+      <c r="D4" s="3">
+        <v>29.72972972972973</v>
+      </c>
+      <c r="E4" s="3">
+        <v>16.21621621621622</v>
+      </c>
+      <c r="F4" s="3">
+        <v>10.81081081081081</v>
+      </c>
+      <c r="G4" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.5218677899691605</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3522690895578711</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.3886789737146608</v>
+      </c>
+      <c r="K4" s="4">
+        <v>80.97904026475472</v>
+      </c>
+      <c r="L4" s="4">
+        <v>73.15647862627738</v>
+      </c>
+      <c r="M4" s="5">
+        <v>37</v>
+      </c>
+      <c r="N4" s="5">
+        <v>749335.476398468</v>
+      </c>
+      <c r="O4" s="4">
+        <v>95.12955140262385</v>
+      </c>
+      <c r="P4" s="5">
+        <v>7877</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>86.48648648648648</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="D5" s="3">
+        <v>10.81081081081081</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>10.81081081081081</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.3187444538563737</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1615366598924374</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2391493660477814</v>
+      </c>
+      <c r="K5" s="4">
+        <v>88.59073359073356</v>
+      </c>
+      <c r="L5" s="4">
+        <v>84.88784086099433</v>
+      </c>
+      <c r="M5" s="5">
+        <v>37</v>
+      </c>
+      <c r="N5" s="5">
+        <v>675609.1914176941</v>
+      </c>
+      <c r="O5" s="4">
+        <v>170.0073456008289</v>
+      </c>
+      <c r="P5" s="5">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>91.8918918918919</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.3082894209055898</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2976492822649814</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.3148912548351748</v>
+      </c>
+      <c r="K6" s="4">
+        <v>87.98952013237728</v>
+      </c>
+      <c r="L6" s="4">
+        <v>86.00519983070407</v>
+      </c>
+      <c r="M6" s="5">
+        <v>37</v>
+      </c>
+      <c r="N6" s="5">
+        <v>364021.1555957794</v>
+      </c>
+      <c r="O6" s="4">
+        <v>92.83885631108886</v>
+      </c>
+      <c r="P6" s="5">
+        <v>3921</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>89.18918918918919</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8.108108108108109</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1835532369648183</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1276621021150257</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1181148070222491</v>
+      </c>
+      <c r="K7" s="4">
+        <v>92.57859900717075</v>
+      </c>
+      <c r="L7" s="4">
+        <v>91.77036096499356</v>
+      </c>
+      <c r="M7" s="5">
+        <v>37</v>
+      </c>
+      <c r="N7" s="5">
+        <v>751143.2349681854</v>
+      </c>
+      <c r="O7" s="4">
+        <v>305.5912265940543</v>
+      </c>
+      <c r="P7" s="5">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>81.08108108108108</v>
+      </c>
+      <c r="C8" s="3">
+        <v>10.81081081081081</v>
+      </c>
+      <c r="D8" s="3">
+        <v>8.108108108108109</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>8.108108108108109</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.28561907108665</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2178273818490055</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2526423290147119</v>
+      </c>
+      <c r="K8" s="4">
+        <v>85.28314028314044</v>
+      </c>
+      <c r="L8" s="4">
+        <v>84.11602878045959</v>
+      </c>
+      <c r="M8" s="5">
+        <v>37</v>
+      </c>
+      <c r="N8" s="5">
+        <v>125424.6127605438</v>
+      </c>
+      <c r="O8" s="4">
+        <v>29.03347517605181</v>
+      </c>
+      <c r="P8" s="5">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>83.78378378378379</v>
+      </c>
+      <c r="C9" s="3">
+        <v>10.81081081081081</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4191350669592918</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3866085480722858</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.4212729958298214</v>
+      </c>
+      <c r="K9" s="4">
+        <v>86.29987129987127</v>
+      </c>
+      <c r="L9" s="4">
+        <v>84.04075216155962</v>
+      </c>
+      <c r="M9" s="5">
+        <v>37</v>
+      </c>
+      <c r="N9" s="5">
+        <v>152498.2495307922</v>
+      </c>
+      <c r="O9" s="4">
+        <v>36.0175364975891</v>
+      </c>
+      <c r="P9" s="5">
+        <v>4234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>91.8918918918919</v>
+      </c>
+      <c r="C10" s="3">
+        <v>8.108108108108109</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1298036793282786</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1062157165440332</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1179628620649082</v>
+      </c>
+      <c r="K10" s="4">
+        <v>92.02518845375998</v>
+      </c>
+      <c r="L10" s="4">
+        <v>90.73311566600181</v>
+      </c>
+      <c r="M10" s="5">
+        <v>37</v>
+      </c>
+      <c r="N10" s="5">
+        <v>230598.0863571167</v>
+      </c>
+      <c r="O10" s="4">
+        <v>86.85426981435657</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>83.78378378378379</v>
+      </c>
+      <c r="C11" s="3">
+        <v>10.81081081081081</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.3262398333704928</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2038547257190012</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2516118378649511</v>
+      </c>
+      <c r="K11" s="4">
+        <v>89.60562603419744</v>
+      </c>
+      <c r="L11" s="4">
+        <v>84.87363202128435</v>
+      </c>
+      <c r="M11" s="5">
+        <v>37</v>
+      </c>
+      <c r="N11" s="5">
+        <v>190515.1612758636</v>
+      </c>
+      <c r="O11" s="4">
+        <v>50.44086875188341</v>
+      </c>
+      <c r="P11" s="5">
+        <v>3777</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>83.78378378378379</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="D12" s="3">
+        <v>13.51351351351351</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="F12" s="3">
+        <v>8.108108108108109</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2742876508815835</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1958222160366665</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2098613143797776</v>
+      </c>
+      <c r="K12" s="4">
+        <v>90.5607648464794</v>
+      </c>
+      <c r="L12" s="4">
+        <v>88.60844065542116</v>
+      </c>
+      <c r="M12" s="5">
+        <v>37</v>
+      </c>
+      <c r="N12" s="5">
+        <v>101907.7589511871</v>
+      </c>
+      <c r="O12" s="4">
+        <v>23.84922980369462</v>
+      </c>
+      <c r="P12" s="5">
+        <v>4273</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>89.18918918918919</v>
+      </c>
+      <c r="C13" s="3">
+        <v>8.108108108108109</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.2499268080592895</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1941630508069041</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2042754062769682</v>
+      </c>
+      <c r="K13" s="4">
+        <v>88.05938591652875</v>
+      </c>
+      <c r="L13" s="4">
+        <v>85.55807485337895</v>
+      </c>
+      <c r="M13" s="5">
+        <v>37</v>
+      </c>
+      <c r="N13" s="5">
+        <v>308316.0121440887</v>
+      </c>
+      <c r="O13" s="4">
+        <v>82.12999790732252</v>
+      </c>
+      <c r="P13" s="5">
+        <v>3754</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>78.37837837837837</v>
+      </c>
+      <c r="C14" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="D14" s="3">
+        <v>16.21621621621622</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="F14" s="3">
+        <v>10.81081081081081</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.2072450745973578</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.103734010291683</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1321272017677485</v>
+      </c>
+      <c r="K14" s="4">
+        <v>86.59404302261417</v>
+      </c>
+      <c r="L14" s="4">
+        <v>86.76522159743735</v>
+      </c>
+      <c r="M14" s="5">
+        <v>37</v>
+      </c>
+      <c r="N14" s="5">
+        <v>2038934.678077698</v>
+      </c>
+      <c r="O14" s="4">
+        <v>340.3897626173118</v>
+      </c>
+      <c r="P14" s="5">
+        <v>5990</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>94.5945945945946</v>
+      </c>
+      <c r="C15" s="3">
+        <v>5.405405405405405</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1329112666010873</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1138618281115224</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.115421163968374</v>
+      </c>
+      <c r="K15" s="4">
+        <v>92.59606545320872</v>
+      </c>
+      <c r="L15" s="4">
+        <v>92.68184291674389</v>
+      </c>
+      <c r="M15" s="5">
+        <v>37</v>
+      </c>
+      <c r="N15" s="5">
+        <v>806542.5078868866</v>
+      </c>
+      <c r="O15" s="4">
+        <v>413.3995427405877</v>
+      </c>
+      <c r="P15" s="5">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>78.37837837837837</v>
+      </c>
+      <c r="C16" s="3">
+        <v>10.81081081081081</v>
+      </c>
+      <c r="D16" s="3">
+        <v>10.81081081081081</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="F16" s="3">
+        <v>8.108108108108109</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.4357021779958912</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1756704117990941</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.2117778563981327</v>
+      </c>
+      <c r="K16" s="4">
+        <v>84.55782312925153</v>
+      </c>
+      <c r="L16" s="4">
+        <v>83.42705121228654</v>
+      </c>
+      <c r="M16" s="5">
+        <v>37</v>
+      </c>
+      <c r="N16" s="5">
+        <v>628819.988489151</v>
+      </c>
+      <c r="O16" s="4">
+        <v>105.9868512538599</v>
+      </c>
+      <c r="P16" s="5">
+        <v>5933</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>94.5945945945946</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2.702702702702703</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.1658778970038707</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.138696455042311</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1270662875895012</v>
+      </c>
+      <c r="K17" s="4">
+        <v>92.61996690568114</v>
+      </c>
+      <c r="L17" s="4">
+        <v>91.02424572223423</v>
+      </c>
+      <c r="M17" s="5">
+        <v>37</v>
+      </c>
+      <c r="N17" s="5">
+        <v>281725.3234386444</v>
+      </c>
+      <c r="O17" s="4">
+        <v>106.1512145586452</v>
+      </c>
+      <c r="P17" s="5">
+        <v>2654</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,16 +5382,16 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>3</v>
       </c>
       <c r="N3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -3253,13 +5429,13 @@
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -3693,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
@@ -3781,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>25</v>
+      </c>
+      <c r="C3" s="5">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5">
+        <v>7</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>6</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>3</v>
+      </c>
+      <c r="N3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5">
+        <v>6</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5">
+        <v>6</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>32</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>4</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>34</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>33</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5">
+        <v>4</v>
+      </c>
+      <c r="D8" s="5">
+        <v>3</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>3</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>31</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>2</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>34</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>31</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>31</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>5</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2</v>
+      </c>
+      <c r="F12" s="5">
+        <v>3</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>3</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>33</v>
+      </c>
+      <c r="C13" s="5">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>29</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2</v>
+      </c>
+      <c r="F14" s="5">
+        <v>4</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>2</v>
+      </c>
+      <c r="I14" s="5">
+        <v>2</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>35</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>29</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4</v>
+      </c>
+      <c r="D16" s="5">
+        <v>4</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>3</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>3</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>35</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,25 +6864,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3868688823883614</v>
+        <v>0.5042777550191033</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4530863159366858</v>
+        <v>0.3881959811228342</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4289257163064257</v>
+        <v>0.4492268529577119</v>
       </c>
       <c r="E3" s="4">
-        <v>85.01308215593929</v>
+        <v>84.97121925693349</v>
       </c>
       <c r="F3" s="4">
-        <v>80.78385819996547</v>
+        <v>81.83445190156566</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
@@ -3946,39 +6909,57 @@
         <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3543577504210684</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4332306027414505</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2068261499615426</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5042777550191033</v>
+        <v>0.3868688823883614</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3881959811228342</v>
+        <v>0.4530863159366858</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4492268529577119</v>
+        <v>0.4289257163064257</v>
       </c>
       <c r="E4" s="4">
-        <v>84.97121925693349</v>
+        <v>85.01308215593929</v>
       </c>
       <c r="F4" s="4">
-        <v>81.83445190156566</v>
+        <v>80.78385819996547</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
@@ -3987,24 +6968,42 @@
         <v>9</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4042197280878289</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3056696420771382</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2518914335409203</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.6758528142596224</v>
@@ -4042,9 +7041,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.5906291885996657</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.567272346247759</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3074793811505798</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7072,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7091,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7133,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,25 +7164,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7248883500871448</v>
+        <v>0.5009056610926254</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4601985426367214</v>
+        <v>0.3293688448819019</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6552067276100567</v>
+        <v>0.2803238836012816</v>
       </c>
       <c r="E3" s="4">
-        <v>82.57980115122972</v>
+        <v>81.57247514390372</v>
       </c>
       <c r="F3" s="4">
-        <v>75.90690070555864</v>
+        <v>74.32455687489325</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
@@ -4168,30 +7218,48 @@
         <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2238498535623243</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4531536572857109</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.327197266288767</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5009056610926254</v>
+        <v>0.7248883500871448</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3293688448819019</v>
+        <v>0.4601985426367214</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2803238836012816</v>
+        <v>0.6552067276100567</v>
       </c>
       <c r="E4" s="4">
-        <v>81.57247514390372</v>
+        <v>82.57980115122972</v>
       </c>
       <c r="F4" s="4">
-        <v>74.32455687489325</v>
+        <v>75.90690070555864</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
@@ -4209,15 +7277,33 @@
         <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.3054392019097129</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7378527555879431</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5194456018142328</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.9410789155588475</v>
@@ -4255,9 +7341,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>1.056777006091309</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3478204419546762</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1627961709081944</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7372,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7391,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7433,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,92 +7464,146 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2804718940770975</v>
+        <v>0.3285969385298634</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1647417862501496</v>
+        <v>0.2534825811020364</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1992388112485169</v>
+        <v>0.3180564597080385</v>
       </c>
       <c r="E3" s="4">
-        <v>89.59968602825745</v>
+        <v>89.11041339612768</v>
       </c>
       <c r="F3" s="4">
-        <v>85.73309241094445</v>
+        <v>87.83772156255378</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2083213373622617</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2780251023783829</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1813363138244107</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3285969385298634</v>
+        <v>0.2804718940770975</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2534825811020364</v>
+        <v>0.1647417862501496</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3180564597080385</v>
+        <v>0.1992388112485169</v>
       </c>
       <c r="E4" s="4">
-        <v>89.11041339612768</v>
+        <v>89.59968602825745</v>
       </c>
       <c r="F4" s="4">
-        <v>87.83772156255378</v>
+        <v>85.73309241094445</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1557750984406089</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2174676584432969</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1186049802175868</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5832825844815659</v>
@@ -4468,9 +7641,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.2462691345898488</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4865580820003627</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1876091742524014</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7672,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7691,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7733,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,34 +7764,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4251840098797223</v>
+        <v>0.2589606869810727</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4395563976257435</v>
+        <v>0.2589606869810727</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4505975450259253</v>
+        <v>0.266808968374398</v>
       </c>
       <c r="E3" s="4">
-        <v>88.3542647828362</v>
+        <v>88.73364730507588</v>
       </c>
       <c r="F3" s="4">
-        <v>87.91946308724863</v>
+        <v>88.80399242815309</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -4599,34 +7823,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.07013990449833002</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2751468187883796</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2751468187883796</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2589606869810727</v>
+        <v>0.4251840098797223</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2589606869810727</v>
+        <v>0.4395563976257435</v>
       </c>
       <c r="D4" s="4">
-        <v>0.266808968374398</v>
+        <v>0.4505975450259253</v>
       </c>
       <c r="E4" s="4">
-        <v>88.73364730507588</v>
+        <v>88.3542647828362</v>
       </c>
       <c r="F4" s="4">
-        <v>88.80399242815309</v>
+        <v>87.91946308724863</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -4640,10 +7882,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2216979687886393</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.38636652839444</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3790292952843011</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.3080560789689999</v>
@@ -4681,9 +7941,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1938606028429446</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2551850054663787</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2216461565943135</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7972,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7991,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8033,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,92 +8064,146 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2969297687520772</v>
+        <v>0.104314906783274</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1512441183359414</v>
+        <v>0.104314906783274</v>
       </c>
       <c r="D3" s="4">
-        <v>0.114825879508157</v>
+        <v>0.1022206176007632</v>
       </c>
       <c r="E3" s="4">
-        <v>92.53532182103608</v>
+        <v>93.98744113029827</v>
       </c>
       <c r="F3" s="4">
-        <v>87.74135260712386</v>
+        <v>94.83479607640668</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.01646738664992908</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1036997889446279</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1036997889446279</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.104314906783274</v>
+        <v>0.2969297687520772</v>
       </c>
       <c r="C4" s="4">
-        <v>0.104314906783274</v>
+        <v>0.1512441183359414</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1022206176007632</v>
+        <v>0.114825879508157</v>
       </c>
       <c r="E4" s="4">
-        <v>93.98744113029827</v>
+        <v>92.53532182103608</v>
       </c>
       <c r="F4" s="4">
-        <v>94.83479607640668</v>
+        <v>87.74135260712386</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.02936162839404517</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2946711819525352</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1512441183359414</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1512482954788471</v>
@@ -4894,9 +8241,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.05108410423216299</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1466042860031959</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1352310930156272</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8272,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2144891386090732</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1552263564765507</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1738239753765995</v>
-      </c>
-      <c r="E3" s="4">
-        <v>87.21873364730507</v>
-      </c>
-      <c r="F3" s="4">
-        <v>86.92651867148528</v>
-      </c>
-      <c r="G3" s="5">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5">
-        <v>11</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3014534870417961</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.320886492086869</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2816534821313113</v>
-      </c>
-      <c r="E4" s="4">
-        <v>87.21350078492934</v>
-      </c>
-      <c r="F4" s="4">
-        <v>87.28187919463082</v>
-      </c>
-      <c r="G4" s="5">
-        <v>13</v>
-      </c>
-      <c r="H4" s="5">
-        <v>11</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4201031444182154</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3071998136110192</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3827695401135152</v>
-      </c>
-      <c r="E5" s="4">
-        <v>80.7142857142851</v>
-      </c>
-      <c r="F5" s="4">
-        <v>77.05308114704002</v>
-      </c>
-      <c r="G5" s="5">
-        <v>11</v>
-      </c>
-      <c r="H5" s="5">
-        <v>8</v>
-      </c>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4709216349330522</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4709216349330522</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4547005884852983</v>
-      </c>
-      <c r="E3" s="4">
-        <v>87.29199372056515</v>
-      </c>
-      <c r="F3" s="4">
-        <v>87.94785751161562</v>
-      </c>
-      <c r="G3" s="5">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5">
-        <v>13</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3718204825305716</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3758384462630687</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3474804236752024</v>
-      </c>
-      <c r="E4" s="4">
-        <v>86.02040816326522</v>
-      </c>
-      <c r="F4" s="4">
-        <v>85.26329375322685</v>
-      </c>
-      <c r="G4" s="5">
-        <v>13</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.485898271964699</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3312568830703455</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6095856722004075</v>
-      </c>
-      <c r="E5" s="4">
-        <v>85.45763760049473</v>
-      </c>
-      <c r="F5" s="4">
-        <v>77.97844213951561</v>
-      </c>
-      <c r="G5" s="5">
-        <v>11</v>
-      </c>
-      <c r="H5" s="5">
-        <v>8</v>
-      </c>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/GrewalHighly2019.xlsx
+++ b/public/downloads/GrewalHighly2019.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.00455466592896188</v>
+        <v>0.09558743320620167</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3011031281241837</v>
+        <v>0.3061714024789032</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3196443104698793</v>
+        <v>0.3090826770205042</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1362650863984908</v>
+        <v>-0.1113190888270879</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1533156729448369</v>
+        <v>0.1549935253988907</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.107705912763997</v>
+        <v>0.1051531933785328</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -1675,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2209853788996794</v>
+        <v>0.2649147278353787</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4236782923917071</v>
+        <v>0.4353468507614386</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2292461249871904</v>
+        <v>0.228816886894684</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01988258396594631</v>
+        <v>0.1242256682293572</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3737547320706148</v>
+        <v>0.3651244478801225</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3803412290617195</v>
+        <v>0.3547110343945491</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.02554609051186346</v>
+        <v>-0.1749470311218033</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4689565510475243</v>
+        <v>0.4574641710006058</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4689565510475243</v>
+        <v>0.4574641710006058</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2270926660967874</v>
+        <v>0.3310965505255012</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4138864360870897</v>
+        <v>0.3974113817542569</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2606271920007313</v>
+        <v>0.2509744778466754</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1267003406779184</v>
+        <v>-0.1443610299567286</v>
       </c>
       <c r="O3" s="5">
         <v>11</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1625831121057453</v>
+        <v>0.160536383091545</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1058971000573586</v>
+        <v>0.1034782384951219</v>
       </c>
       <c r="R3" s="5">
         <v>11</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1179564969620081</v>
+        <v>-0.08622368852070394</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09332336342422322</v>
+        <v>0.09088237815950749</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09332336342422322</v>
+        <v>0.09088237815950749</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1142442108926588</v>
+        <v>-0.1251135296038228</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1341774502960652</v>
+        <v>0.13255797148842</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1233262537351284</v>
+        <v>0.122631758917835</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -2457,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.0388693512076775</v>
+        <v>0.09924863335933765</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2908082855801839</v>
+        <v>0.2939128427283759</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1933750372824462</v>
+        <v>0.1917067006803492</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -2516,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.01668601463357401</v>
+        <v>0.02608255861571251</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3747823898792709</v>
+        <v>0.378072280129216</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1927292678344562</v>
+        <v>0.1888412157208847</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1664667616284063</v>
+        <v>0.1370975900609892</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3107450048850295</v>
+        <v>0.3010108908629237</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2348717629650832</v>
+        <v>0.2280208546435532</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.20353152080755</v>
+        <v>-0.200503639873034</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1829528153453314</v>
+        <v>0.1827199014272917</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1829528153453314</v>
+        <v>0.1827199014272917</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -2816,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.008153519798993456</v>
+        <v>-0.03204036531980137</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.388641751438307</v>
+        <v>0.3794545031610732</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1370872128877243</v>
+        <v>0.1344331189409679</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1808436494333421</v>
+        <v>-0.2105328080053255</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2470830649482991</v>
+        <v>0.2443840505326643</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.273146353517537</v>
+        <v>0.2698475581206499</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1008862157071988</v>
+        <v>-0.1191895514819521</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2558467616932276</v>
+        <v>0.2536089494110697</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1431252811057024</v>
+        <v>0.1422262624479274</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1175250070288148</v>
+        <v>-0.2617832652807692</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.286204057978525</v>
+        <v>0.2384195322626331</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2499729139518254</v>
+        <v>0.2102278659472721</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -3175,16 +3175,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.05245829710125349</v>
+        <v>0.01355595753420857</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2000573856782663</v>
+        <v>0.186439551189631</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.187800259548611</v>
+        <v>0.1711562396180568</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -3357,13 +3357,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.07006799245865736</v>
+        <v>0.07750412721763311</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.145301511657242</v>
+        <v>0.144729501291167</v>
       </c>
       <c r="Q3" s="4">
         <v>0.08054384455965931</v>
@@ -3416,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.004840695012796914</v>
+        <v>0.02693014800582993</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3142772027246289</v>
+        <v>0.3148494128571941</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1014056200644551</v>
+        <v>0.09994054793748645</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -3475,16 +3475,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1234496039221816</v>
+        <v>0.07296109482762603</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1539585884670834</v>
+        <v>0.144050706808888</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1320879613575182</v>
+        <v>0.1199783282197239</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3924718418312927</v>
+        <v>-0.3818442969352454</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1145425451338265</v>
+        <v>0.1125653830991494</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1145425451338265</v>
+        <v>0.1125653830991494</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2890922684858808</v>
+        <v>-0.2763237927271689</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1017213773815874</v>
+        <v>0.09907846442560352</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1017213773815874</v>
+        <v>0.09907846442560352</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.6091966209738323</v>
+        <v>-0.5858550285198447</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1914805337763497</v>
+        <v>0.1936024967267122</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1304147768003226</v>
+        <v>0.1278212665276573</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -3957,13 +3957,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.01224682374932335</v>
+        <v>0.007121169477255052</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5465610686477543</v>
+        <v>0.5453782253542001</v>
       </c>
       <c r="Q3" s="4">
         <v>0.1750321536949674</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.006260776759032538</v>
+        <v>0.02500496665716234</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5289175897019928</v>
+        <v>0.5317503873588075</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1560045722715189</v>
+        <v>0.1540639522559392</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -4075,16 +4075,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1484313496688606</v>
+        <v>0.1950295332080216</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1945234570273875</v>
+        <v>0.1902872585238274</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.198230520278763</v>
+        <v>0.1930529443299673</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -4257,16 +4257,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.235761793892172</v>
+        <v>-0.2188918708371581</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1960323857886554</v>
+        <v>0.1967627476694031</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1321529801907916</v>
+        <v>0.1315383786403504</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -4316,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2721860610884841</v>
+        <v>-0.3301911051587947</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1408941663535148</v>
+        <v>0.1294007996906797</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1259252627413653</v>
+        <v>0.1183078691958199</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -4375,16 +4375,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3844317407329647</v>
+        <v>-0.4092810677750407</v>
       </c>
       <c r="O5" s="5">
         <v>11</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1597670010268184</v>
+        <v>0.1575079712957206</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1597670010268184</v>
+        <v>0.1575079712957206</v>
       </c>
       <c r="R5" s="5">
         <v>11</v>
@@ -4521,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4282621349018109</v>
+        <v>0.4202426419597239</v>
       </c>
       <c r="I3" s="4">
-        <v>0.251232556783049</v>
+        <v>0.2477076912306916</v>
       </c>
       <c r="J3" s="4">
-        <v>0.296099365614682</v>
+        <v>0.3018079487268132</v>
       </c>
       <c r="K3" s="4">
         <v>83.04467733039171</v>
@@ -4571,13 +4571,13 @@
         <v>2.702702702702703</v>
       </c>
       <c r="H4" s="4">
-        <v>0.5218677899691605</v>
+        <v>0.5176429011715463</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3522690895578711</v>
+        <v>0.3294598313655257</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3886789737146608</v>
+        <v>0.3895341057379043</v>
       </c>
       <c r="K4" s="4">
         <v>80.97904026475472</v>
@@ -4621,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.3187444538563737</v>
+        <v>0.3092531274830966</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1615366598924374</v>
+        <v>0.1461675693813032</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2391493660477814</v>
+        <v>0.2454782859112286</v>
       </c>
       <c r="K5" s="4">
         <v>88.59073359073356</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.3082894209055898</v>
+        <v>0.2891268625728518</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2976492822649814</v>
+        <v>0.268782167749316</v>
       </c>
       <c r="J6" s="4">
-        <v>0.3148912548351748</v>
+        <v>0.2939511808930634</v>
       </c>
       <c r="K6" s="4">
         <v>87.98952013237728</v>
@@ -4721,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1835532369648183</v>
+        <v>0.1852259876647024</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1276621021150257</v>
+        <v>0.1270296844401096</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1181148070222491</v>
+        <v>0.1168087664231475</v>
       </c>
       <c r="K7" s="4">
         <v>92.57859900717075</v>
@@ -4771,13 +4771,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.28561907108665</v>
+        <v>0.2914583627239769</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2178273818490055</v>
+        <v>0.2129043223182293</v>
       </c>
       <c r="J8" s="4">
-        <v>0.2526423290147119</v>
+        <v>0.2460608910631168</v>
       </c>
       <c r="K8" s="4">
         <v>85.28314028314044</v>
@@ -4821,13 +4821,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4191350669592918</v>
+        <v>0.4071669525607107</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3866085480722858</v>
+        <v>0.3710303351524764</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4212729958298214</v>
+        <v>0.3939721095015571</v>
       </c>
       <c r="K9" s="4">
         <v>86.29987129987127</v>
@@ -4871,13 +4871,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1298036793282786</v>
+        <v>0.1277454481793595</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1062157165440332</v>
+        <v>0.1042955626087732</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1179628620649082</v>
+        <v>0.1157093041380749</v>
       </c>
       <c r="K10" s="4">
         <v>92.02518845375998</v>
@@ -4921,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.3262398333704928</v>
+        <v>0.3255926053146178</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2038547257190012</v>
+        <v>0.2000613102658822</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2516118378649511</v>
+        <v>0.2493593399702447</v>
       </c>
       <c r="K11" s="4">
         <v>89.60562603419744</v>
@@ -4971,13 +4971,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2742876508815835</v>
+        <v>0.2701754544731906</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1958222160366665</v>
+        <v>0.193996284261592</v>
       </c>
       <c r="J12" s="4">
-        <v>0.2098613143797776</v>
+        <v>0.2083124268214255</v>
       </c>
       <c r="K12" s="4">
         <v>90.5607648464794</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.2499268080592895</v>
+        <v>0.2283028466174075</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1941630508069041</v>
+        <v>0.1748441120395426</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2042754062769682</v>
+        <v>0.2000726909901233</v>
       </c>
       <c r="K13" s="4">
         <v>88.05938591652875</v>
@@ -5071,13 +5071,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.2072450745973578</v>
+        <v>0.2042995583466611</v>
       </c>
       <c r="I14" s="4">
-        <v>0.103734010291683</v>
+        <v>0.09947065099824043</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1321272017677485</v>
+        <v>0.129199975601131</v>
       </c>
       <c r="K14" s="4">
         <v>86.59404302261417</v>
@@ -5121,13 +5121,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1329112666010873</v>
+        <v>0.1319188508598817</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1138618281115224</v>
+        <v>0.1114788976163058</v>
       </c>
       <c r="J15" s="4">
-        <v>0.115421163968374</v>
+        <v>0.1146825479500213</v>
       </c>
       <c r="K15" s="4">
         <v>92.59606545320872</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.4357021779958912</v>
+        <v>0.4350224813251676</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1756704117990941</v>
+        <v>0.1733943985682335</v>
       </c>
       <c r="J16" s="4">
-        <v>0.2117778563981327</v>
+        <v>0.2102092167382679</v>
       </c>
       <c r="K16" s="4">
         <v>84.55782312925153</v>
@@ -5221,13 +5221,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.1658778970038707</v>
+        <v>0.1614246972955136</v>
       </c>
       <c r="I17" s="4">
-        <v>0.138696455042311</v>
+        <v>0.1351640759510563</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1270662875895012</v>
+        <v>0.123135374992886</v>
       </c>
       <c r="K17" s="4">
         <v>92.61996690568114</v>
@@ -6924,16 +6924,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3543577504210684</v>
+        <v>0.3134236194011919</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4332306027414505</v>
+        <v>0.4237842648137867</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2068261499615426</v>
+        <v>0.2022779131815563</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -6983,16 +6983,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4042197280878289</v>
+        <v>0.41455617694578</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3056696420771382</v>
+        <v>0.3064647535277498</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2518914335409203</v>
+        <v>0.2507429392233702</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -7042,16 +7042,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5906291885996657</v>
+        <v>0.553778129668558</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.567272346247759</v>
+        <v>0.5505218649154373</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3074793811505798</v>
+        <v>0.3022149441604216</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -7224,13 +7224,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2238498535623243</v>
+        <v>-0.1382815960132007</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4531536572857109</v>
+        <v>0.4676581674938037</v>
       </c>
       <c r="Q3" s="4">
         <v>0.327197266288767</v>
@@ -7283,16 +7283,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3054392019097129</v>
+        <v>0.1648542518749991</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7378527555879431</v>
+        <v>0.7122072537890679</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5194456018142328</v>
+        <v>0.4601985426367214</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -7342,16 +7342,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>1.056777006091309</v>
+        <v>1.073116218071263</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3478204419546762</v>
+        <v>0.3467760787881712</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1627961709081944</v>
+        <v>0.1581583031062763</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -7524,16 +7524,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2083213373622617</v>
+        <v>-0.2963525244923062</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2780251023783829</v>
+        <v>0.2589020236448002</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1813363138244107</v>
+        <v>0.1532837129355258</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -7583,16 +7583,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1557750984406089</v>
+        <v>-0.1294747817331086</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2174676584432969</v>
+        <v>0.2162067725859607</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1186049802175868</v>
+        <v>0.1123329666211894</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -7642,16 +7642,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2462691345898488</v>
+        <v>-0.3324566707191536</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4865580820003627</v>
+        <v>0.4787228514431531</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1876091742524014</v>
+        <v>0.1780327813491454</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -7824,16 +7824,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.07013990449833002</v>
+        <v>-0.06852103307676316</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2751468187883796</v>
+        <v>0.2457636472566181</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2751468187883796</v>
+        <v>0.2457636472566181</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -7883,16 +7883,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2216979687886393</v>
+        <v>0.4077910218225043</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.38636652839444</v>
+        <v>0.3732382201562573</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3790292952843011</v>
+        <v>0.3492992069401145</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -7942,16 +7942,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1938606028429446</v>
+        <v>0.2774166642144564</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2551850054663787</v>
+        <v>0.240969967166194</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2216461565943135</v>
+        <v>0.194675089539926</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -8124,16 +8124,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01646738664992908</v>
+        <v>-0.01223195927616416</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1036997889446279</v>
+        <v>0.1033739868389537</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1036997889446279</v>
+        <v>0.1033739868389537</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -8183,13 +8183,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.02936162839404517</v>
+        <v>0.01970353016844228</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2946711819525352</v>
+        <v>0.2984454249188804</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1512441183359414</v>
@@ -8242,16 +8242,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.05108410423216299</v>
+        <v>0.08478050483762445</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1466042860031959</v>
+        <v>0.1481553809765589</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1352310930156272</v>
+        <v>0.1335676574257803</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
